--- a/Documentos Base/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 5 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE4F830-E8EB-4CAF-B6AB-01FC1408E8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD4E799-E5BF-46EA-8D81-3EA4586DA911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1455" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 05" sheetId="1" r:id="rId1"/>
-    <sheet name="Resumen Velocidad" sheetId="2" r:id="rId2"/>
-    <sheet name="Glosario" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId2"/>
+    <sheet name="Resumen Velocidad" sheetId="2" r:id="rId3"/>
+    <sheet name="Glosario" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="161">
   <si>
     <t>SPRINT BACKLOG — Sprint 05: Módulo de Planilla Mensual y Cierre Contable</t>
   </si>
@@ -397,13 +398,121 @@
   </si>
   <si>
     <t>Documento de resultados de pruebas del sprint</t>
+  </si>
+  <si>
+    <t>SPRINT BACKLOG — Sprint 03: Catalogo de Materiales, Gestion de Bodega e Inventario</t>
+  </si>
+  <si>
+    <t>ICARO CONSTRUCTORES BMGM S.A.S.  |  Sistema de Gestion Integral de Obra</t>
+  </si>
+  <si>
+    <t>Sprint N°:</t>
+  </si>
+  <si>
+    <t>Fecha de cierre:</t>
+  </si>
+  <si>
+    <t>Scrum Master:</t>
+  </si>
+  <si>
+    <t>Ivan Santiago Pulgar Leon</t>
+  </si>
+  <si>
+    <t>Estado:</t>
+  </si>
+  <si>
+    <t>Cerrado – 100% completado</t>
+  </si>
+  <si>
+    <t>SP Real</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Criterios de Aceptación</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Evidencia / Ref.</t>
+  </si>
+  <si>
+    <t>Isaac Sebastian Castro Muesmueran / Ivan Santiago Pulgar Leon</t>
+  </si>
+  <si>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>El sistema permite generar una planilla mensual de obra mediante POST /api/v1/planillas. La ruta está protegida por autenticación JWT. Sin token retorna 401. Roles no autorizados como Bodeguero y Residente reciben 403. Un rol autorizado como Admin pasa RBAC y no recibe 401 ni 403. La planilla debe consolidar información del proyecto, periodo, avances físicos, rubros, valores económicos y horas-hombre cuando existan datos disponibles. Si la BD o los datos requeridos no están disponibles, el endpoint puede retornar 400 o 500 sin invalidar la prueba de permisos.</t>
+  </si>
+  <si>
+    <t>Completado. Se validó la protección de la ruta, la restricción por roles y el flujo base de generación de planilla. La generación queda preparada para integrarse con cierre mensual, PDF y almacenamiento del archivo generado.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/planillas.routes.js, backend/src/controllers/planillas.controller.js, backend/src/services/planillas.service.js, backend/tests/planilla_contable.test.js – Tests 1, 2, 3 y 4</t>
+  </si>
+  <si>
+    <t>Ejecutar cierre contable mensual consolidando gastos, avances y materiales por proyecto</t>
+  </si>
+  <si>
+    <t>El sistema permite crear cierres contables mediante POST /api/v1/cierres-contables. La ruta está protegida por autenticación. Sin token retorna 401. Roles operativos no autorizados como Residente y Bodeguero reciben 403. Admin pasa RBAC y no recibe 401 ni 403. El cierre debe consolidar información mensual por proyecto, incluyendo avances, gastos, materiales y consumos cuando existan datos disponibles. Si faltan campos obligatorios, registros base o conexión a BD, el endpoint puede retornar 400 o 500 de forma controlada.</t>
+  </si>
+  <si>
+    <t>Completado. Se validó la capa de seguridad y permisos del cierre contable. El flujo queda alineado con la regla funcional de consolidación mensual, bloqueo de periodo e integridad del cierre.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/cierres-contables.routes.js, backend/src/controllers/cierres-contables.controller.js, backend/src/services/cierres-contables.service.js, backend/tests/planilla_contable.test.js – Tests 11, 12, 13 y 14</t>
+  </si>
+  <si>
+    <t>GET /api/v1/planillas permite consultar el historial de planillas generadas. La ruta está protegida por autenticación. Sin token retorna 401. Roles con permiso de lectura, como Residente, pasan RBAC y no reciben 401 ni 403. El endpoint queda preparado para filtrar por proyecto, periodo, estado de generación o usuario generador, según parámetros disponibles. La consulta puede retornar 200 o 500 dependiendo de la disponibilidad de BD.</t>
+  </si>
+  <si>
+    <t>Completado. La consulta de historial de planillas fue validada a nivel de autenticación y RBAC. La respuesta funcional depende de la existencia de registros de planillas y de la conexión con BD.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/planillas.routes.js, backend/src/controllers/planillas.controller.js, backend/src/services/planillas.service.js, backend/tests/planilla_contable.test.js – Tests 5 y 6</t>
+  </si>
+  <si>
+    <t>El sistema permite registrar gastos mediante POST /api/v1/gastos. La ruta está protegida por autenticación. Sin token retorna 401. Admin pasa RBAC y no recibe 401 ni 403. El gasto debe asociarse al proyecto, periodo o cierre contable correspondiente, con detalle de rubro, descripción, monto y observación cuando aplique. Si faltan campos o no existe disponibilidad de BD, el endpoint puede retornar 400 o 500 de forma controlada.</t>
+  </si>
+  <si>
+    <t>Completado. Se validó la protección de la ruta y la autorización para registrar gastos operativos. El flujo queda preparado para alimentar el cierre contable mensual y la posterior generación de planilla.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/gastos.routes.js, backend/src/controllers/gastos.controller.js, backend/src/services/gastos.service.js, backend/tests/planilla_contable.test.js – Tests 17 y 18</t>
+  </si>
+  <si>
+    <t>El backend integra PDFKit como dependencia para la generación de planillas mensuales. El servicio de planillas queda preparado para construir documentos PDF con datos del proyecto, periodo, avances, valores económicos, horas-hombre y anexos cuando existan evidencias disponibles. La descarga del PDF se protege mediante GET /api/v1/planillas//pdf. Sin token retorna 401. Bodeguero recibe 403. Presidente y Admin pasan RBAC y no reciben 401 ni 403.</t>
+  </si>
+  <si>
+    <t>Completado. La generación y consulta de PDF quedaron cubiertas por pruebas de acceso. La integración queda preparada para conectarse con StorageService, QueueService y auditoría cuando el flujo asíncrono esté habilitado.</t>
+  </si>
+  <si>
+    <t>backend/package.json, backend/src/services/planillas.service.js, backend/src/controllers/planillas.controller.js, backend/tests/planilla_contable.test.js – Tests 7, 8, 9 y 10</t>
+  </si>
+  <si>
+    <t>18 casos de prueba automatizados en planilla_contable.test.js. Grupo 1: creación y consulta de planillas con autenticación y RBAC. Grupo 2: descarga/consulta de PDF de planilla con autenticación y RBAC. Grupo 3: creación y consulta de cierres contables con autenticación y RBAC. Grupo 4: registro de gastos contables con autenticación y RBAC. Todos los casos deben finalizar en PASS.</t>
+  </si>
+  <si>
+    <t>18/18 pruebas PASS. La suite valida seguridad, permisos por rol, control de acceso a PDF, cierre contable y registro de gastos. También confirma comportamiento esperado ante BD no disponible, registros inexistentes o validaciones de negocio pendientes.</t>
+  </si>
+  <si>
+    <t>backend/test</t>
+  </si>
+  <si>
+    <t>Implementar el módulo de Planilla Mensual de Obra con generación de PDF, consulta de historial por proyecto y periodo, el módulo de Cierre Contable Mensual con consolidación de avances, gastos y materiales por proyecto, el registro de gastos operativos asociados al cierre contable, la integración de PDFKit para generación de documentos en backend y la cobertura de ambos módulos con pruebas automatizadas de integración</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,8 +566,33 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,8 +624,14 @@
         <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -514,11 +654,76 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -550,23 +755,98 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -883,7 +1163,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12"/>
@@ -893,7 +1173,7 @@
       <c r="F1" s="12"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="12"/>
@@ -906,7 +1186,7 @@
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="12"/>
@@ -918,7 +1198,7 @@
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="12"/>
@@ -930,7 +1210,7 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="12"/>
@@ -942,7 +1222,7 @@
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="12"/>
@@ -970,7 +1250,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -990,7 +1270,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1010,7 +1290,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
@@ -1030,7 +1310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
@@ -1050,7 +1330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>31</v>
       </c>
@@ -1070,7 +1350,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
@@ -1091,7 +1371,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="12"/>
@@ -1117,6 +1397,449 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3547449E-F765-40AD-8CC7-9ECB59135B7A}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.5703125" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" customWidth="1"/>
+    <col min="6" max="6" width="4.42578125" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="49.28515625" customWidth="1"/>
+    <col min="11" max="11" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="44.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+    </row>
+    <row r="3" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="30"/>
+    </row>
+    <row r="4" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="20">
+        <v>46123</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="20">
+        <v>46157</v>
+      </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="22"/>
+    </row>
+    <row r="5" spans="1:12" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
+    </row>
+    <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="28">
+        <v>22</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="22"/>
+    </row>
+    <row r="7" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="39">
+        <v>5</v>
+      </c>
+      <c r="G8" s="39">
+        <v>5</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="L8" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="39">
+        <v>5</v>
+      </c>
+      <c r="G9" s="39">
+        <v>5</v>
+      </c>
+      <c r="H9" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="I9" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="L9" s="39" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="39">
+        <v>3</v>
+      </c>
+      <c r="G10" s="39">
+        <v>3</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="I10" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J10" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="K10" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="L10" s="39" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="39">
+        <v>3</v>
+      </c>
+      <c r="G11" s="39">
+        <v>3</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="39">
+        <v>3</v>
+      </c>
+      <c r="G12" s="39">
+        <v>3</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="L12" s="39" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="111" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="39">
+        <v>3</v>
+      </c>
+      <c r="G13" s="39">
+        <v>3</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="K13" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="L13" s="39" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="25">
+        <v>22</v>
+      </c>
+      <c r="G14" s="25">
+        <v>22</v>
+      </c>
+      <c r="H14" s="36"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1338,7 +2061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Documentos Base/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
@@ -1,32 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 5 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD4E799-E5BF-46EA-8D81-3EA4586DA911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16E28E3-FA90-410F-A132-BB52838C0CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Backlog Sprint 05" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId2"/>
-    <sheet name="Resumen Velocidad" sheetId="2" r:id="rId3"/>
-    <sheet name="Glosario" sheetId="3" r:id="rId4"/>
+    <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
+    <sheet name="Resumen Velocidad" sheetId="2" r:id="rId2"/>
+    <sheet name="Glosario" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="161">
-  <si>
-    <t>SPRINT BACKLOG — Sprint 05: Módulo de Planilla Mensual y Cierre Contable</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="155">
   <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.</t>
   </si>
@@ -34,21 +30,12 @@
     <t>Proyecto:</t>
   </si>
   <si>
-    <t>ICARO CONSTRUCTORES BMGM S.A.S. — Sistema de Gestión Integral de Obra</t>
-  </si>
-  <si>
     <t>Fecha de inicio:</t>
   </si>
   <si>
-    <t>11/04/2026</t>
-  </si>
-  <si>
     <t>Objetivo:</t>
   </si>
   <si>
-    <t>Implementar el módulo de Planilla Mensual de Obra con generación de PDF, el módulo de Cierre Contable Mensual con consolidación de gastos por proyecto, y cubrir ambos módulos con pruebas automatizadas de integración.</t>
-  </si>
-  <si>
     <t>Vel. estimada (SP):</t>
   </si>
   <si>
@@ -94,9 +81,6 @@
     <t>HU-17</t>
   </si>
   <si>
-    <t>Ejecutar cierre contable mensual (consolidar gastos, avances y materiales por proyecto)</t>
-  </si>
-  <si>
     <t>Contabilidad</t>
   </si>
   <si>
@@ -109,9 +93,6 @@
     <t>Media</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>HU-19</t>
   </si>
   <si>
@@ -241,9 +222,6 @@
     <t>Grupos 1, 2, 3 y 4 PASS</t>
   </si>
   <si>
-    <t>Compromisos Sprint 04 §8.3 cum.</t>
-  </si>
-  <si>
     <t>5/5</t>
   </si>
   <si>
@@ -400,9 +378,6 @@
     <t>Documento de resultados de pruebas del sprint</t>
   </si>
   <si>
-    <t>SPRINT BACKLOG — Sprint 03: Catalogo de Materiales, Gestion de Bodega e Inventario</t>
-  </si>
-  <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.  |  Sistema de Gestion Integral de Obra</t>
   </si>
   <si>
@@ -506,6 +481,12 @@
   </si>
   <si>
     <t>Implementar el módulo de Planilla Mensual de Obra con generación de PDF, consulta de historial por proyecto y periodo, el módulo de Cierre Contable Mensual con consolidación de avances, gastos y materiales por proyecto, el registro de gastos operativos asociados al cierre contable, la integración de PDFKit para generación de documentos en backend y la cobertura de ambos módulos con pruebas automatizadas de integración</t>
+  </si>
+  <si>
+    <t>Compromisos Sprint 04 cerrados</t>
+  </si>
+  <si>
+    <t>SPRINT BACKLOG — Sprint 05</t>
   </si>
 </sst>
 </file>
@@ -519,17 +500,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -556,12 +526,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -581,18 +545,40 @@
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,17 +602,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -723,64 +704,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -789,22 +791,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -813,10 +800,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -825,28 +812,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1150,253 +1125,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="58" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3547449E-F765-40AD-8CC7-9ECB59135B7A}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1416,410 +1144,410 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="32"/>
+    </row>
+    <row r="4" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="33">
+        <v>46123</v>
+      </c>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="33">
+        <v>46157</v>
+      </c>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
+    </row>
+    <row r="5" spans="1:12" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="29"/>
+    </row>
+    <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="37">
+        <v>22</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="29"/>
+    </row>
+    <row r="7" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="H7" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-    </row>
-    <row r="3" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="26" t="s">
+      <c r="I7" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="J7" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="13">
+        <v>5</v>
+      </c>
+      <c r="G8" s="13">
+        <v>5</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="13">
+        <v>5</v>
+      </c>
+      <c r="G9" s="13">
+        <v>5</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="30"/>
-    </row>
-    <row r="4" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="20">
-        <v>46123</v>
-      </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="H4" s="20">
-        <v>46157</v>
-      </c>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="22"/>
-    </row>
-    <row r="5" spans="1:12" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="H5" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
-    </row>
-    <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="28">
+      <c r="C10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="26" t="s">
+      <c r="F10" s="13">
+        <v>3</v>
+      </c>
+      <c r="G10" s="13">
+        <v>3</v>
+      </c>
+      <c r="H10" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="I10" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21"/>
-      <c r="L6" s="22"/>
-    </row>
-    <row r="7" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="J10" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="J7" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="L7" s="23" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="125.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
+      <c r="D11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="39">
-        <v>5</v>
-      </c>
-      <c r="G8" s="39">
-        <v>5</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I8" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="J8" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="K8" s="39" t="s">
-        <v>142</v>
-      </c>
-      <c r="L8" s="39" t="s">
+      <c r="F11" s="13">
+        <v>3</v>
+      </c>
+      <c r="G11" s="13">
+        <v>3</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="J11" s="21" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="135.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39" t="s">
+      <c r="K11" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="108" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="13">
+        <v>3</v>
+      </c>
+      <c r="G12" s="13">
+        <v>3</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="111" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="13">
+        <v>3</v>
+      </c>
+      <c r="G13" s="13">
+        <v>3</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="7">
         <v>22</v>
       </c>
-      <c r="B9" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="39">
-        <v>5</v>
-      </c>
-      <c r="G9" s="39">
-        <v>5</v>
-      </c>
-      <c r="H9" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I9" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="J9" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="K9" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="L9" s="39" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="39">
-        <v>3</v>
-      </c>
-      <c r="G10" s="39">
-        <v>3</v>
-      </c>
-      <c r="H10" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I10" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="J10" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="K10" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="L10" s="39" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="138.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="39">
-        <v>3</v>
-      </c>
-      <c r="G11" s="39">
-        <v>3</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I11" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="J11" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="K11" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="L11" s="39" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="39">
-        <v>3</v>
-      </c>
-      <c r="G12" s="39">
-        <v>3</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I12" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="K12" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="L12" s="39" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="111" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="39">
-        <v>3</v>
-      </c>
-      <c r="G13" s="39">
-        <v>3</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="K13" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="L13" s="39" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="25">
+      <c r="G14" s="7">
         <v>22</v>
       </c>
-      <c r="G14" s="25">
-        <v>22</v>
-      </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1839,7 +1567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1850,207 +1578,207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D6" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="C11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="B12" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C12" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="9" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="B13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="2" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="C14" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="9" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="B15" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="C15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -2061,7 +1789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2072,186 +1800,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B5" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C5" s="17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="9" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B6" s="19" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="C6" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="B7" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C7" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="9" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="B8" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C8" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="B9" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C9" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="9" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="B10" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C10" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="2" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="B11" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C11" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="9" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="B12" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C12" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="B13" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="C13" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="9" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="B14" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C14" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="B15" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C15" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C13" s="9" t="s">
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="B16" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C16" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="B17" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="C17" s="17" t="s">
         <v>117</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Documentos Base/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 5 documentacion/Sprint_05_Backlog_ICARO.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 5 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16E28E3-FA90-410F-A132-BB52838C0CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621B4B35-6123-4AED-9B95-86DDA2FEB777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPRINT BACKLOG" sheetId="4" r:id="rId1"/>
     <sheet name="Resumen Velocidad" sheetId="2" r:id="rId2"/>
-    <sheet name="Glosario" sheetId="3" r:id="rId3"/>
+    <sheet name="Resumen de casos de prueba " sheetId="5" r:id="rId3"/>
+    <sheet name="Glosario" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="223">
   <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.</t>
   </si>
@@ -487,13 +488,217 @@
   </si>
   <si>
     <t>SPRINT BACKLOG — Sprint 05</t>
+  </si>
+  <si>
+    <t>ID CP</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Evidencia</t>
+  </si>
+  <si>
+    <t>Grupo 1</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Grupo 2</t>
+  </si>
+  <si>
+    <t>Grupo 3</t>
+  </si>
+  <si>
+    <t>Grupo 4</t>
+  </si>
+  <si>
+    <t>CP-069</t>
+  </si>
+  <si>
+    <t>Planillas</t>
+  </si>
+  <si>
+    <t>POST /planillas sin token → ruta protegida</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 01</t>
+  </si>
+  <si>
+    <t>CP-070</t>
+  </si>
+  <si>
+    <t>POST /planillas con Bodeguero → RBAC deniega creación</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 02</t>
+  </si>
+  <si>
+    <t>CP-071</t>
+  </si>
+  <si>
+    <t>POST /planillas con Residente → RBAC deniega creación</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 03</t>
+  </si>
+  <si>
+    <t>CP-072</t>
+  </si>
+  <si>
+    <t>POST /planillas con Admin → pasa RBAC y procesa planilla</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 04</t>
+  </si>
+  <si>
+    <t>CP-073</t>
+  </si>
+  <si>
+    <t>GET /planillas sin token → ruta protegida</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 05</t>
+  </si>
+  <si>
+    <t>CP-074</t>
+  </si>
+  <si>
+    <t>GET /planillas con Residente → pasa RBAC para acceso de lectura</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 06</t>
+  </si>
+  <si>
+    <t>CP-075</t>
+  </si>
+  <si>
+    <t>Planilla PDF</t>
+  </si>
+  <si>
+    <t>GET /planillas/:id/pdf sin token → ruta protegida</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 07</t>
+  </si>
+  <si>
+    <t>CP-076</t>
+  </si>
+  <si>
+    <t>GET /planillas/:id/pdf con Bodeguero → RBAC deniega acceso al PDF</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 08</t>
+  </si>
+  <si>
+    <t>CP-077</t>
+  </si>
+  <si>
+    <t>GET /planillas/:id/pdf con Presidente/Gerente → pasa RBAC</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 09</t>
+  </si>
+  <si>
+    <t>CP-078</t>
+  </si>
+  <si>
+    <t>GET /planillas/:id/pdf con Admin → pasa RBAC</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 10</t>
+  </si>
+  <si>
+    <t>CP-079</t>
+  </si>
+  <si>
+    <t>Cierre Contable</t>
+  </si>
+  <si>
+    <t>POST /cierres-contables sin token → ruta protegida</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 11</t>
+  </si>
+  <si>
+    <t>CP-080</t>
+  </si>
+  <si>
+    <t>POST /cierres-contables con Residente → RBAC deniega ejecución de cierre</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 12</t>
+  </si>
+  <si>
+    <t>CP-081</t>
+  </si>
+  <si>
+    <t>POST /cierres-contables con Bodeguero → RBAC deniega ejecución de cierre</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 13</t>
+  </si>
+  <si>
+    <t>CP-082</t>
+  </si>
+  <si>
+    <t>POST /cierres-contables con Admin → pasa RBAC</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 14</t>
+  </si>
+  <si>
+    <t>CP-083</t>
+  </si>
+  <si>
+    <t>GET /cierres-contables sin token → ruta protegida</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 15</t>
+  </si>
+  <si>
+    <t>CP-084</t>
+  </si>
+  <si>
+    <t>GET /cierres-contables con Contador → pasa RBAC para lectura</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 16</t>
+  </si>
+  <si>
+    <t>CP-085</t>
+  </si>
+  <si>
+    <t>Gastos</t>
+  </si>
+  <si>
+    <t>POST /gastos sin token → ruta protegida</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 17</t>
+  </si>
+  <si>
+    <t>CP-086</t>
+  </si>
+  <si>
+    <t>POST /gastos con Admin → pasa RBAC y registra gasto</t>
+  </si>
+  <si>
+    <t>planilla_contable.test.js – Test 18</t>
+  </si>
+  <si>
+    <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 05 (CP-69 a CP-086)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -506,35 +711,41 @@
       <sz val="9"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -577,8 +788,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -611,8 +829,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -700,11 +928,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -769,60 +1012,81 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1144,36 +1408,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
     </row>
     <row r="3" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
@@ -1189,7 +1453,7 @@
       <c r="G3" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="38" t="s">
         <v>17</v>
       </c>
       <c r="I3" s="31"/>
@@ -1201,7 +1465,7 @@
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="39">
         <v>46123</v>
       </c>
       <c r="C4" s="28"/>
@@ -1211,7 +1475,7 @@
       <c r="G4" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="H4" s="33">
+      <c r="H4" s="39">
         <v>46157</v>
       </c>
       <c r="I4" s="28"/>
@@ -1223,13 +1487,13 @@
       <c r="A5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="36"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="26"/>
       <c r="G5" s="8" t="s">
         <v>121</v>
       </c>
@@ -1245,7 +1509,7 @@
       <c r="A6" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="30">
         <v>22</v>
       </c>
       <c r="C6" s="31"/>
@@ -1530,13 +1794,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="7">
         <v>22</v>
       </c>
@@ -1551,17 +1815,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1578,7 +1842,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="22" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="23"/>
@@ -1790,6 +2054,416 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61526623-C3FE-44B7-8154-23D8BA6BD0C9}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="57.5703125" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="43" t="s">
+        <v>171</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="47" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="47" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="43" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" s="44" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F19" s="44" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="46" t="s">
+        <v>219</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1800,7 +2474,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="40" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="23"/>
